--- a/final_elitech_and_teh_delivery_2026-04-27/pictures_for_import.xlsx
+++ b/final_elitech_and_teh_delivery_2026-04-27/pictures_for_import.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205819/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205819/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205819/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205819/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205819/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205819/gallery_06.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205819/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205819/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205819/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205819/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205819/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205819/gallery_06.webp</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205859/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205859/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205859/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205859/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205859/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205859/gallery_06.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205859/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205859/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205859/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205859/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205859/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205859/gallery_06.webp</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205862/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205862/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205862/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205862/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205862/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205862/gallery_06.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205862/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205862/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205862/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205862/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205862/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205862/gallery_06.webp</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/204252/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204252/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204252/gallery_03.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/204252/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204252/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204252/gallery_03.webp</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/215238/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/215238/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/215238/gallery_03.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/215238/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/215238/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/215238/gallery_03.webp</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/204251/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204251/gallery_02.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/204251/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204251/gallery_02.webp</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/215237/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/215237/gallery_02.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/215237/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/215237/gallery_02.webp</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205731/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205731/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205731/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205731/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205731/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205731/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205731/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205731/gallery_08.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205731/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205731/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205731/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205731/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205731/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205731/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205731/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205731/gallery_08.webp</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210303/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210303/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210303/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210303/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210303/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210303/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210303/gallery_07.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210303/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210303/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210303/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210303/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210303/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210303/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210303/gallery_07.webp</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_10.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210304/gallery_10.webp</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/214178/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214178/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214178/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214178/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214178/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214178/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214178/gallery_07.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/214178/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214178/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214178/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214178/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214178/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214178/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214178/gallery_07.webp</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_10.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214180/gallery_10.webp</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_11.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214184/gallery_11.webp</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_11.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214185/gallery_11.webp</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205583/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205583/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205583/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205583/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205583/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205583/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205583/gallery_07.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205583/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205583/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205583/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205583/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205583/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205583/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205583/gallery_07.webp</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205584/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205584/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205584/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205584/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205584/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205584/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205584/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205584/gallery_08.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205584/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205584/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205584/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205584/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205584/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205584/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205584/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205584/gallery_08.webp</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205582/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205582/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205582/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205582/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205582/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205582/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205582/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205582/gallery_08.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205582/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205582/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205582/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205582/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205582/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205582/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205582/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205582/gallery_08.webp</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205587/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205587/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205587/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205587/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205587/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205587/gallery_06.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205587/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205587/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205587/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205587/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205587/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205587/gallery_06.webp</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_13.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205726/gallery_13.webp</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_12.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205776/gallery_12.webp</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_11.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198648/gallery_11.webp</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_12.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/198651/gallery_12.webp</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_11.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205968/gallery_11.webp</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_11.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205969/gallery_11.webp</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_11.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207362/gallery_11.webp</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_13.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207363/gallery_13.webp</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_13.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207364/gallery_13.webp</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_13.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204005/gallery_13.webp</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_14.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210312/gallery_14.webp</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_14.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204882/gallery_14.webp</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/206078/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206078/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206078/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206078/gallery_04.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/206078/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206078/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206078/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206078/gallery_04.webp</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_10.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204860/gallery_10.webp</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_11.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204867/gallery_11.webp</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_13.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210283/gallery_13.webp</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_11.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205751/gallery_11.webp</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_14.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204508/gallery_14.webp</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_14.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205359/gallery_14.webp</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_14.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205361/gallery_14.webp</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_14.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_15.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_14.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/191146/gallery_15.webp</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_14.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_15.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_14.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207403/gallery_15.webp</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_14.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210334/gallery_14.webp</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_14.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_15.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_16.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_14.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_15.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210335/gallery_16.webp</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_14.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207354/gallery_14.webp</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_14.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207355/gallery_14.webp</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_13.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207397/gallery_13.webp</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_13.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207398/gallery_13.webp</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_13.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207399/gallery_13.webp</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_13.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207400/gallery_13.webp</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_13.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207401/gallery_13.webp</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_14.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_15.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_14.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207402/gallery_15.webp</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/206080/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206080/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206080/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206080/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206080/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206080/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206080/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206080/gallery_08.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/206080/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206080/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206080/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206080/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206080/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206080/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206080/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206080/gallery_08.webp</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/206081/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206081/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206081/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206081/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206081/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206081/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206081/gallery_07.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/206081/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206081/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206081/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206081/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206081/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206081/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206081/gallery_07.webp</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_14.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_15.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_14.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/185682/gallery_15.webp</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_09.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214945/gallery_09.webp</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_09.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/179473/gallery_09.webp</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_13.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207387/gallery_13.webp</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_12.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/204520/gallery_12.webp</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_12.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205697/gallery_12.webp</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_11.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205225/gallery_11.webp</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_12.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205226/gallery_12.webp</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_11.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/205228/gallery_11.webp</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_14.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206452/gallery_14.webp</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_14.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207405/gallery_14.webp</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_14.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207388/gallery_14.webp</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_14.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207393/gallery_14.webp</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/206083/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206083/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206083/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206083/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/206083/gallery_05.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/206083/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206083/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206083/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206083/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/206083/gallery_05.webp</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_12.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210314/gallery_12.webp</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_14.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210315/gallery_14.webp</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_14.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210316/gallery_14.webp</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_12.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210317/gallery_12.webp</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_14.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210318/gallery_14.webp</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_10.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_11.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_12.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_13.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_14.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_10.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_11.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_12.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_13.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/210319/gallery_14.webp</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_10.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/207374/gallery_10.webp</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_02.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_03.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_04.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_05.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_06.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_07.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_08.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_09.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_10.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_02.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_03.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_04.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_05.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_06.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_07.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_08.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_09.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/LPS508-01/gallery_10.webp</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/214190/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214190/gallery_02.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/214190/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214190/gallery_02.webp</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/214191/gallery_01.webp|/final_elitech_and_teh_delivery_2026-04-27/import_images/214191/gallery_02.webp</t>
+          <t>/final_elitech_and_teh_delivery_2026-04-27/import_images/214191/gallery_01.webp;/final_elitech_and_teh_delivery_2026-04-27/import_images/214191/gallery_02.webp</t>
         </is>
       </c>
     </row>
